--- a/Books1.xlsx
+++ b/Books1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yyusuf5\Downloads\CODE_LOCAL\CoratCoret\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D830A7-3EC0-47DA-BD36-7AB21B94AFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36099354-CFEE-430C-BE65-CB2959C9186F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{764FC0BB-F6C2-4BED-B0DC-BBEE2B907A44}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="308">
   <si>
     <t>Taiwan</t>
   </si>
@@ -958,6 +958,9 @@
   </si>
   <si>
     <t>Zhanna.Imanbekova@pmi.com</t>
+  </si>
+  <si>
+    <t>email_single</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CB8EB3-BA67-4E2E-8531-C2317F1A27F7}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -1379,7 +1382,7 @@
     <col min="4" max="4" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -1392,8 +1395,11 @@
       <c r="D1" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1407,8 +1413,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C2,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>MinJung.Kim@pmi.com</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1422,8 +1431,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C3,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Hamlet.Unusyan@pmi.com</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1437,8 +1449,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C4,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Mohammed.Abdelfattah@pmi.com</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1452,8 +1467,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C5,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Ankit.Rohatgi@pmi.com</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1467,8 +1485,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C6,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Solmaz.Azimi@swma.se</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1482,8 +1503,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C7,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Danny.Chang@pmi.com</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1497,8 +1521,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C8,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Hamlet.Unusyan@pmi.com</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1512,8 +1539,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C9,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Rafik.Bhura@smpmi.com</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1527,8 +1557,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C10,PIC!D:D,PIC!E:E,"notfound")</f>
         <v>Danijal.Morankic@pmi.com</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1541,8 +1574,11 @@
       <c r="D11" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1556,8 +1592,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C12,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>stefan.verschelden@pmi.com</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1571,8 +1610,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C13,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Danijal.Morankic@pmi.com</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -1586,8 +1628,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C14,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Daniel.Diaz@pmi.com</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -1601,8 +1646,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C15,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Zainab.Imran@pmi.com</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1616,8 +1664,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C16,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Mohammed.Abdelfattah@pmi.com</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1631,8 +1682,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C17,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Adam.Cellar@pmi.com</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1646,8 +1700,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C18,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>stefan.verschelden@pmi.com</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1661,8 +1718,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C19,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Ingrid.Wijaya@sampoerna.com</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1676,8 +1736,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C20,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>wilhelm.su@pmi.com</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1691,8 +1754,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C21,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Mohammed.Abdelfattah@pmi.com</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1705,8 +1771,11 @@
       <c r="D22" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1720,8 +1789,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C23,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Mohammed.Abdelfattah@pmi.com</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1735,8 +1807,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C24,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Laura.PerezMonge@pmi.com</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1750,8 +1825,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C25,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Levent.Asici@pmi.com</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1765,8 +1843,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C26,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Guilherme.Pedroso@pmi.com</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -1780,8 +1861,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C27,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Mohammed.Abdelfattah@pmi.com</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1795,8 +1879,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C28,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Michael.Koeniger@pmi.com</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -1809,8 +1896,11 @@
       <c r="D29" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1824,8 +1914,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C30,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Mohammed.Abdelfattah@pmi.com</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1839,8 +1932,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C31,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Levent.Asici@pmi.com</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1854,8 +1950,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C32,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Xavier.Lachat@pmi.com</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -1869,8 +1968,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C33,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>Adam.Cellar@pmi.com</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -1883,8 +1985,11 @@
       <c r="D34" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -1898,8 +2003,11 @@
         <f>_xlfn.XLOOKUP(Sheet1!C35,PIC!D:D,PIC!E:E,"    notfound")</f>
         <v>diogo.algarvio@pmi.com</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>304</v>
       </c>
@@ -1909,12 +2017,18 @@
       <c r="D36" s="3" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>305</v>
       </c>
       <c r="D37" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1953,7 +2067,7 @@
         <v>90</v>
       </c>
       <c r="E1" s="1" t="str">
-        <f t="shared" ref="E1:E64" si="0">IF(F1="","",TRIM(_xlfn.LET(
+        <f t="shared" ref="E1" si="0">IF(F1="","",TRIM(_xlfn.LET(
         _xlpm.text,F1,
         _xlpm.startPos,IF(ISNUMBER(SEARCH("DEL =",_xlpm.text)),SEARCH("DEL =",_xlpm.text)+6,IF(ISNUMBER(SEARCH("=",_xlpm.text)),SEARCH("=",_xlpm.text)+2,1)),
         _xlpm.endPos,IFERROR(SEARCH(";",_xlpm.text,_xlpm.startPos),LEN(_xlpm.text)+1),
